--- a/сетевые контроллеры/109/соединения стенда.xlsx
+++ b/сетевые контроллеры/109/соединения стенда.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ремонт\fixing\сетевые контроллеры\109\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{949DFE90-BAFC-4FA0-A049-778EA049B67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D6CB57-112F-4D66-B8F0-A15FC1547B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{E2F75D83-A7AE-4FD6-A58F-5129EB2519E9}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="15">
   <si>
     <t>ZUMM</t>
   </si>
@@ -61,6 +61,15 @@
   </si>
   <si>
     <t>EMHL</t>
+  </si>
+  <si>
+    <t>BAT</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
 </sst>
 </file>
@@ -112,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -120,7 +129,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -342,6 +357,9 @@
           </a:avLst>
         </a:prstGeom>
         <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
           <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
@@ -393,7 +411,7 @@
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 73988"/>
+            <a:gd name="adj1" fmla="val 67446"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -507,6 +525,9 @@
           </a:avLst>
         </a:prstGeom>
         <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="00B050"/>
+          </a:solidFill>
           <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
@@ -560,6 +581,9 @@
           <a:avLst/>
         </a:prstGeom>
         <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
           <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
@@ -613,6 +637,9 @@
           <a:avLst/>
         </a:prstGeom>
         <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
           <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
@@ -666,6 +693,9 @@
           <a:avLst/>
         </a:prstGeom>
         <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
           <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
@@ -690,13 +720,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>586740</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -743,13 +773,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>579120</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -796,13 +826,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>601980</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -851,13 +881,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>594360</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>68580</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -879,6 +909,171 @@
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
             <a:gd name="adj1" fmla="val 40491"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>594360</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Соединитель: уступ 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02E68B4D-CB10-F874-AA23-765A9CB27754}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="4853940"/>
+          <a:ext cx="2423160" cy="731520"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 24843"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Соединитель: уступ 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D5EDAB2-5108-779A-7B8D-D35A7669747C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1226820" y="3025140"/>
+          <a:ext cx="3665220" cy="1112520"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 76611"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>594360</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="Соединитель: уступ 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32BC9311-B739-D554-049C-73E15754BF39}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1203960" y="4297680"/>
+          <a:ext cx="2484120" cy="1082040"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -1202,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E75EBE1-F5C0-46BC-9171-865B2F56D453}">
-  <dimension ref="B3:I31"/>
+  <dimension ref="B3:I34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
@@ -1322,65 +1517,87 @@
         <v>7</v>
       </c>
     </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B22" s="5"/>
+      <c r="I22" s="5"/>
+    </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="5"/>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="5"/>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G26" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B24" s="3" t="s">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B27" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G27" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B25" s="3" t="s">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B28" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G28" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B26" s="3" t="s">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B29" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G29" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="G27" s="1" t="s">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="G28" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="G29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="G30" s="1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="G31" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B33" s="3"/>
+      <c r="G33" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B34" s="3"/>
+      <c r="G34" s="1" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>